--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_3_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_3_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319439.7096585986</v>
+        <v>312765.6093280502</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>3001330.373596265</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745724</v>
+        <v>20361635.87782001</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813416.085193352</v>
+        <v>4805098.675066959</v>
       </c>
     </row>
     <row r="11">
@@ -1165,19 +1165,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>12.91010078545518</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1211,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>23.5527513075609</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1405,19 +1405,19 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1496,13 +1496,13 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1530,19 +1530,19 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1557,19 +1557,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1606,16 +1606,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>22.90079999999999</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="15">
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1730,19 +1730,19 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V15" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W15" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1764,10 +1764,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1794,19 +1794,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T16" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1846,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1879,22 +1879,22 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1919,19 +1919,19 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1961,13 +1961,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>22.02246762618611</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2037,28 +2037,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2113,10 +2113,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>40.463693489693</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>45.20536318881176</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2204,16 +2204,16 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>26.37147235617635</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2232,64 +2232,64 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2305,25 +2305,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>52.41298284430552</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2350,10 +2350,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>69.03881051849277</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>29.7578455661223</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -2447,10 +2447,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2545,19 +2545,19 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>94.38361247260485</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>82.46119763909351</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>29.75784556612239</v>
+        <v>53.57063283035821</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2678,19 +2678,19 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2782,22 +2782,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>21.18375537072436</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2824,31 +2824,31 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>52.41298284430547</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,13 +2858,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>117.8074216906837</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
         <v>157.6450804554009</v>
@@ -2879,7 +2879,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>87.90265002780788</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>215</v>
+        <v>202.2946864288972</v>
       </c>
     </row>
     <row r="33">
@@ -3095,31 +3095,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>34.47584603422613</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>88.46061606973225</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3155,13 +3155,13 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3198,10 +3198,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3216,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>14.83685490770591</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>17.56289348969292</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3313,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>179.7283339446665</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="36">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -3344,19 +3344,19 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>32.06583114665507</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>6.672679130316409</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3389,19 +3389,19 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3496,25 +3496,25 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>167.4320114308426</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>179.7283339446664</v>
       </c>
       <c r="H38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3547,19 +3547,19 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="39">
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>139.4012633594442</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>88.12509107326176</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>47.02492433367367</v>
       </c>
     </row>
     <row r="41">
@@ -3730,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3781,22 +3781,22 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>190.9324654410926</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>177.6197007854553</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3809,22 +3809,22 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>10.29751456419317</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3854,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>58.6665359729289</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -3866,16 +3866,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -3939,13 +3939,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>15.12050584389412</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>50.83706245038672</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>100.8903465994381</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>74.62772033681188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L11" t="n">
-        <v>52.52000000000001</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M11" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>80.86787878787879</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S11" t="n">
-        <v>54.60525252525252</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T11" t="n">
-        <v>28.34262626262626</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="V11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L12" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="M12" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N12" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O12" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="W12" t="n">
-        <v>104</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="X12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y12" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H13" t="n">
-        <v>2.08</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I13" t="n">
-        <v>2.08</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J13" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.3</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>100.8903465994381</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.62772033681188</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R13" t="n">
-        <v>48.36509407418561</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S13" t="n">
-        <v>22.10246781155935</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.08</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F14" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G14" t="n">
-        <v>54.60525252525252</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H14" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>26.78000000000001</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L14" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M14" t="n">
-        <v>26.78000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N14" t="n">
-        <v>52.52000000000001</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M15" t="n">
-        <v>27.82</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O15" t="n">
-        <v>52.52000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V15" t="n">
-        <v>80.86787878787879</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="W15" t="n">
-        <v>54.60525252525252</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X15" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="F16" t="n">
-        <v>2.44072336510073</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>74.98844370191262</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R16" t="n">
-        <v>48.72581743928635</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S16" t="n">
-        <v>22.46319117666009</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="V16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="X16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.44072336510073</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>28.84</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>56.56</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M17" t="n">
-        <v>84.28</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N17" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>83.71717171717171</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="S17" t="n">
-        <v>55.43434343434343</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T17" t="n">
-        <v>30.52282828282829</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="X17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E18" t="n">
-        <v>30.52282828282829</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="F18" t="n">
-        <v>30.52282828282829</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="G18" t="n">
-        <v>30.52282828282829</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="H18" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L18" t="n">
-        <v>28.84</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M18" t="n">
-        <v>28.84</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N18" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S18" t="n">
-        <v>87.08848484848485</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T18" t="n">
-        <v>58.80565656565657</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y18" t="n">
-        <v>30.52282828282829</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24.48491679412739</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>81.05057335978395</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>81.05057335978395</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="T19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="U19" t="n">
-        <v>81.05057335978395</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="V19" t="n">
-        <v>81.05057335978395</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="W19" t="n">
-        <v>81.05057335978395</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="X19" t="n">
-        <v>81.05057335978395</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>52.76774507695567</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>274.7843326814268</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="C20" t="n">
-        <v>274.7843326814268</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D20" t="n">
-        <v>274.7843326814268</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E20" t="n">
-        <v>274.7843326814268</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F20" t="n">
-        <v>274.7843326814268</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G20" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>802.5254372164702</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V20" t="n">
-        <v>802.5254372164702</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W20" t="n">
-        <v>761.6530195501136</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="X20" t="n">
-        <v>518.2186761157702</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="Y20" t="n">
-        <v>518.2186761157702</v>
+        <v>233.7108255783361</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>473.9864226398218</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="C21" t="n">
-        <v>473.9864226398218</v>
+        <v>338.3038493798764</v>
       </c>
       <c r="D21" t="n">
-        <v>325.0520129785705</v>
+        <v>338.3038493798764</v>
       </c>
       <c r="E21" t="n">
-        <v>165.814557973115</v>
+        <v>179.0663943744209</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>179.0663943744209</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>179.0663943744209</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>65.69725878200022</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>851.7806659261865</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O21" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>735.7763817363891</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>500.6242735046464</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W21" t="n">
-        <v>473.9864226398218</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X21" t="n">
-        <v>473.9864226398218</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y21" t="n">
-        <v>473.9864226398218</v>
+        <v>512.7568786610034</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>559.0910937821268</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C23" t="n">
-        <v>315.6567503477834</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D23" t="n">
-        <v>72.22240691343993</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X23" t="n">
-        <v>802.5254372164702</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y23" t="n">
-        <v>802.5254372164702</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.28</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="C24" t="n">
-        <v>19.28</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>249.2431058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>933.94157013523</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>705.717951871619</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V24" t="n">
-        <v>470.5658436398763</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W24" t="n">
-        <v>227.1315002055328</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X24" t="n">
-        <v>19.28</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.28</v>
+        <v>257.2326523711826</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>601.4856691642474</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="C26" t="n">
-        <v>506.1486868686869</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="D26" t="n">
-        <v>262.7143434343434</v>
+        <v>114.6452713866835</v>
       </c>
       <c r="E26" t="n">
-        <v>262.7143434343434</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F26" t="n">
-        <v>262.7143434343434</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>812.6170525846973</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S26" t="n">
-        <v>601.4856691642474</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T26" t="n">
-        <v>601.4856691642474</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="U26" t="n">
-        <v>601.4856691642474</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="V26" t="n">
-        <v>601.4856691642474</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="W26" t="n">
-        <v>601.4856691642474</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="X26" t="n">
-        <v>601.4856691642474</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="Y26" t="n">
-        <v>601.4856691642474</v>
+        <v>358.0940480307835</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>49.33842986477009</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="C27" t="n">
-        <v>49.33842986477009</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="D27" t="n">
-        <v>49.33842986477009</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="E27" t="n">
-        <v>49.33842986477009</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="F27" t="n">
-        <v>49.33842986477009</v>
+        <v>212.1237188612924</v>
       </c>
       <c r="G27" t="n">
-        <v>49.33842986477009</v>
+        <v>73.39289344390789</v>
       </c>
       <c r="H27" t="n">
-        <v>49.33842986477009</v>
+        <v>73.39289344390789</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>613.1906659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N27" t="n">
-        <v>725.41</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O27" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U27" t="n">
-        <v>735.7763817363891</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V27" t="n">
-        <v>500.6242735046464</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="W27" t="n">
-        <v>257.1899300703029</v>
+        <v>627.7355178317791</v>
       </c>
       <c r="X27" t="n">
-        <v>49.33842986477009</v>
+        <v>419.8840176262463</v>
       </c>
       <c r="Y27" t="n">
-        <v>49.33842986477009</v>
+        <v>212.1237188612924</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>40.6788758079141</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>802.5254372164702</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T29" t="n">
-        <v>802.5254372164702</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U29" t="n">
-        <v>749.5830303030303</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="V29" t="n">
-        <v>749.5830303030303</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="W29" t="n">
-        <v>506.1486868686869</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="X29" t="n">
-        <v>506.1486868686869</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="Y29" t="n">
-        <v>262.7143434343434</v>
+        <v>527.5764290961142</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>694.6151335328177</v>
+        <v>845.059759863481</v>
       </c>
       <c r="C30" t="n">
-        <v>520.1621042516907</v>
+        <v>670.606730582354</v>
       </c>
       <c r="D30" t="n">
-        <v>520.1621042516907</v>
+        <v>521.6723209211027</v>
       </c>
       <c r="E30" t="n">
-        <v>360.9246492462352</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="F30" t="n">
-        <v>360.9246492462352</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G30" t="n">
-        <v>222.1938238288507</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H30" t="n">
-        <v>108.82468823643</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>249.2431058683491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N30" t="n">
-        <v>487.8331058683492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O30" t="n">
-        <v>726.4231058683491</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P30" t="n">
-        <v>909.0665834817</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C32" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D32" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E32" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S32" t="n">
-        <v>668.7151515151515</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T32" t="n">
-        <v>451.5434343434343</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U32" t="n">
-        <v>234.3717171717172</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V32" t="n">
-        <v>234.3717171717172</v>
+        <v>710.516763498309</v>
       </c>
       <c r="W32" t="n">
-        <v>234.3717171717172</v>
+        <v>467.067986854209</v>
       </c>
       <c r="X32" t="n">
-        <v>234.3717171717172</v>
+        <v>467.067986854209</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>758.8304705528857</v>
+        <v>109.3894334091926</v>
       </c>
       <c r="C33" t="n">
-        <v>724.006383649627</v>
+        <v>109.3894334091926</v>
       </c>
       <c r="D33" t="n">
-        <v>575.0719739883757</v>
+        <v>109.3894334091926</v>
       </c>
       <c r="E33" t="n">
-        <v>415.8345189829203</v>
+        <v>109.3894334091926</v>
       </c>
       <c r="F33" t="n">
-        <v>269.2999610098052</v>
+        <v>109.3894334091926</v>
       </c>
       <c r="G33" t="n">
-        <v>130.5691355924207</v>
+        <v>109.3894334091926</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>109.3894334091926</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>17.2</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>17.2</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M33" t="n">
-        <v>182.2619638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N33" t="n">
-        <v>395.1119638733197</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O33" t="n">
-        <v>607.9619638733197</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>758.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>758.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>758.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U33" t="n">
-        <v>758.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V33" t="n">
-        <v>758.8304705528857</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W33" t="n">
-        <v>758.8304705528857</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X33" t="n">
-        <v>758.8304705528857</v>
+        <v>277.6047704292607</v>
       </c>
       <c r="Y33" t="n">
-        <v>758.8304705528857</v>
+        <v>277.6047704292607</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>39.69443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>148.9833604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>133.9966383258138</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>133.9966383258138</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>133.9966383258138</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>133.9966383258138</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>133.9966383258138</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V34" t="n">
-        <v>133.9966383258138</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W34" t="n">
-        <v>133.9966383258138</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>133.9966383258138</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>264.1820028730358</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C35" t="n">
-        <v>47.01028570131862</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D35" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E35" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F35" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G35" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H35" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>719.4169572236606</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R35" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S35" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T35" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U35" t="n">
-        <v>698.5254372164702</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="V35" t="n">
-        <v>698.5254372164702</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="W35" t="n">
-        <v>698.5254372164702</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="X35" t="n">
-        <v>698.5254372164702</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="Y35" t="n">
-        <v>481.353720044753</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>49.58972843096473</v>
+        <v>228.3944971323047</v>
       </c>
       <c r="C36" t="n">
-        <v>49.58972843096473</v>
+        <v>228.3944971323047</v>
       </c>
       <c r="D36" t="n">
-        <v>49.58972843096473</v>
+        <v>228.3944971323047</v>
       </c>
       <c r="E36" t="n">
-        <v>49.58972843096473</v>
+        <v>228.3944971323047</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>228.3944971323047</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>221.6544172026922</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>108.2852816102715</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>17.2</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M36" t="n">
-        <v>182.2619638733197</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N36" t="n">
-        <v>395.1119638733197</v>
+        <v>782.3092529910735</v>
       </c>
       <c r="O36" t="n">
-        <v>607.9619638733197</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="P36" t="n">
-        <v>790.6054414866707</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U36" t="n">
-        <v>642.8282828282828</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V36" t="n">
-        <v>642.8282828282828</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W36" t="n">
-        <v>425.6565656565656</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="X36" t="n">
-        <v>217.8050654510328</v>
+        <v>436.1547958972586</v>
       </c>
       <c r="Y36" t="n">
-        <v>217.8050654510328</v>
+        <v>228.3944971323047</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>632.7366674600557</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="C38" t="n">
-        <v>632.7366674600557</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="D38" t="n">
-        <v>415.5649502883385</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="E38" t="n">
-        <v>246.4417064188005</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="F38" t="n">
-        <v>246.4417064188005</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="G38" t="n">
-        <v>246.4417064188005</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H38" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>29.26998924708335</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>113.210609091369</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>293.2864606760276</v>
       </c>
       <c r="M38" t="n">
-        <v>513.1408574955809</v>
+        <v>506.5265183822256</v>
       </c>
       <c r="N38" t="n">
-        <v>718.9953797028202</v>
+        <v>712.3810405894649</v>
       </c>
       <c r="O38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U38" t="n">
-        <v>632.7366674600557</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="V38" t="n">
-        <v>632.7366674600557</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="W38" t="n">
-        <v>632.7366674600557</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="X38" t="n">
-        <v>632.7366674600557</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="Y38" t="n">
-        <v>632.7366674600557</v>
+        <v>198.7752914759215</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>556.6438759116518</v>
+        <v>653.815691967159</v>
       </c>
       <c r="C39" t="n">
-        <v>556.6438759116518</v>
+        <v>653.815691967159</v>
       </c>
       <c r="D39" t="n">
-        <v>415.8345189829203</v>
+        <v>504.8812823059077</v>
       </c>
       <c r="E39" t="n">
-        <v>415.8345189829203</v>
+        <v>504.8812823059077</v>
       </c>
       <c r="F39" t="n">
-        <v>269.2999610098052</v>
+        <v>358.3467243327926</v>
       </c>
       <c r="G39" t="n">
-        <v>130.5691355924207</v>
+        <v>219.6158989154081</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>106.2467633229875</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="M39" t="n">
-        <v>182.2619638733197</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="N39" t="n">
-        <v>395.1119638733197</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="O39" t="n">
-        <v>607.9619638733197</v>
+        <v>782.3092529910735</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>758.8304705528857</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T39" t="n">
-        <v>556.6438759116518</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U39" t="n">
-        <v>556.6438759116518</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V39" t="n">
-        <v>556.6438759116518</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W39" t="n">
-        <v>556.6438759116518</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X39" t="n">
-        <v>556.6438759116518</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y39" t="n">
-        <v>556.6438759116518</v>
+        <v>653.815691967159</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>860</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="R40" t="n">
-        <v>860</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="S40" t="n">
-        <v>860</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="T40" t="n">
-        <v>860</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="U40" t="n">
-        <v>725.4677095097293</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="V40" t="n">
-        <v>725.4677095097293</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="W40" t="n">
-        <v>725.4677095097293</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="X40" t="n">
-        <v>725.4677095097293</v>
+        <v>64.73144338400959</v>
       </c>
       <c r="Y40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.04</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="C41" t="n">
-        <v>17.04</v>
+        <v>445.2559140063055</v>
       </c>
       <c r="D41" t="n">
-        <v>17.04</v>
+        <v>445.2559140063055</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>445.2559140063055</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>445.2559140063055</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>445.2559140063055</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>17.04</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>197.1158515846586</v>
+        <v>300.1647985849684</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>511.4548195661379</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>717.3093417733771</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>626.7568694802578</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>411.6053543287427</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>411.6053543287427</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="W41" t="n">
-        <v>411.6053543287427</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="X41" t="n">
-        <v>232.1915151515151</v>
+        <v>660.8359782662478</v>
       </c>
       <c r="Y41" t="n">
-        <v>17.04</v>
+        <v>660.8359782662478</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>636.8484848484849</v>
+        <v>269.9280347519783</v>
       </c>
       <c r="C42" t="n">
-        <v>462.3954555673579</v>
+        <v>269.9280347519783</v>
       </c>
       <c r="D42" t="n">
-        <v>313.4610459061066</v>
+        <v>269.9280347519783</v>
       </c>
       <c r="E42" t="n">
-        <v>313.4610459061066</v>
+        <v>269.9280347519783</v>
       </c>
       <c r="F42" t="n">
-        <v>166.9264879329916</v>
+        <v>269.9280347519783</v>
       </c>
       <c r="G42" t="n">
-        <v>28.1956625156071</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="H42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>565.0115431095638</v>
       </c>
       <c r="N42" t="n">
-        <v>775.0075600578374</v>
+        <v>776.3015640907333</v>
       </c>
       <c r="O42" t="n">
-        <v>782.6054414866707</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>693.2683977768746</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>693.2683977768746</v>
       </c>
       <c r="U42" t="n">
-        <v>852</v>
+        <v>693.2683977768746</v>
       </c>
       <c r="V42" t="n">
-        <v>852</v>
+        <v>477.6883335169322</v>
       </c>
       <c r="W42" t="n">
-        <v>636.8484848484849</v>
+        <v>477.6883335169322</v>
       </c>
       <c r="X42" t="n">
-        <v>636.8484848484849</v>
+        <v>477.6883335169322</v>
       </c>
       <c r="Y42" t="n">
-        <v>636.8484848484849</v>
+        <v>269.9280347519783</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>151.5722904902707</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="U43" t="n">
-        <v>151.5722904902707</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8433,10 +8433,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
         <v>230.3462332272727</v>
@@ -8445,10 +8445,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>256.1824907047645</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,13 +8512,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
@@ -8530,7 +8530,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>260.7159099194822</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M11" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N11" t="n">
-        <v>229.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8752,10 +8752,10 @@
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M12" t="n">
-        <v>167.0835288715133</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8764,10 +8764,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>159.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>245.0393459944755</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N14" t="n">
-        <v>255.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O14" t="n">
-        <v>256.0982114216868</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
-        <v>164.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M15" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N15" t="n">
-        <v>156.2912070328283</v>
+        <v>155.926839997373</v>
       </c>
       <c r="O15" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>246.9585379136674</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>255.8883403615407</v>
       </c>
       <c r="O17" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L18" t="n">
-        <v>165.423066648561</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869681</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,10 +9381,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M20" t="n">
         <v>449.5135334928325</v>
@@ -9466,16 +9466,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O21" t="n">
-        <v>255.9491071452661</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
         <v>139.9817740860215</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N24" t="n">
-        <v>357.73449794694</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9870,7 +9870,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9940,16 +9940,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>244.694574784155</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>312.5030352242461</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>195.4700735994558</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10332,10 +10332,10 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
-        <v>318.8224416842694</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10408,22 +10408,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>308.8632903597151</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
         <v>210.0772877358491</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
-        <v>380.8001812627454</v>
+        <v>373.6931947635578</v>
       </c>
       <c r="P35" t="n">
-        <v>321.7987081714826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,22 +10645,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>308.8632903597151</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>152.5681426542525</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
         <v>210.0772877358491</v>
@@ -10803,19 +10803,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>317.0384260719773</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>372.5271208127775</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
         <v>231.2329957552695</v>
@@ -10882,22 +10882,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>308.8632903597151</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P39" t="n">
-        <v>318.4627686399372</v>
+        <v>143.9463056241383</v>
       </c>
       <c r="Q39" t="n">
         <v>210.0772877358491</v>
@@ -11040,19 +11040,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>442.643829968084</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O41" t="n">
-        <v>380.8001812627454</v>
+        <v>277.2978653650641</v>
       </c>
       <c r="P41" t="n">
         <v>321.7987081714826</v>
@@ -11122,16 +11122,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>150.2708721503366</v>
+        <v>150.6779938033424</v>
       </c>
       <c r="P42" t="n">
         <v>133.9744074143302</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>238.4355521223813</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23069,13 +23069,13 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>119.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>89.33464423649647</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
         <v>89.39663285141508</v>
@@ -23105,7 +23105,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
         <v>171.6831711038378</v>
@@ -23157,13 +23157,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>131.8977236196974</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,10 +23178,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
         <v>177.2933913771695</v>
@@ -23263,19 +23263,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>126.9683179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S11" t="n">
-        <v>183.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T11" t="n">
-        <v>197.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U11" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>327.7522584701349</v>
+        <v>305.1859059859041</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23306,19 +23306,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.9150037196417</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23342,7 +23342,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>77.59148166841231</v>
       </c>
       <c r="S12" t="n">
         <v>171.6831711038378</v>
@@ -23354,13 +23354,13 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>232.8005871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W12" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X12" t="n">
-        <v>205.7729852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y12" t="n">
         <v>205.6826957773044</v>
@@ -23388,19 +23388,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.9909793584588</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H13" t="n">
-        <v>162.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I13" t="n">
-        <v>155.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23415,19 +23415,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>382.7338416634806</v>
+        <v>357.1135504688497</v>
       </c>
       <c r="C14" t="n">
         <v>365.2728917710076</v>
@@ -23464,16 +23464,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>383.9752457417114</v>
+        <v>384.3096932574806</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23515,13 +23515,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
-        <v>349.240968717413</v>
+        <v>323.6206775227822</v>
       </c>
       <c r="X14" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y14" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="15">
@@ -23579,7 +23579,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>100.1578341526431</v>
+        <v>74.5375429580123</v>
       </c>
       <c r="S15" t="n">
         <v>171.6831711038378</v>
@@ -23588,19 +23588,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V15" t="n">
-        <v>209.8997871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W15" t="n">
-        <v>225.6949831609196</v>
+        <v>229.1286306766888</v>
       </c>
       <c r="X15" t="n">
-        <v>179.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y15" t="n">
-        <v>179.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="16">
@@ -23622,10 +23622,10 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F16" t="n">
-        <v>145.4210480229312</v>
+        <v>122.8546955387004</v>
       </c>
       <c r="G16" t="n">
-        <v>167.9909793584588</v>
+        <v>142.3706881638279</v>
       </c>
       <c r="H16" t="n">
         <v>162.2271725074396</v>
@@ -23652,19 +23652,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>151.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S16" t="n">
-        <v>198.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T16" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U16" t="n">
         <v>286.3190293564909</v>
@@ -23704,10 +23704,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
         <v>210.4758895704059</v>
@@ -23737,22 +23737,22 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>121.8691179411497</v>
+        <v>125.5678236918632</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>198.4334495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>223.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
-        <v>349.240968717413</v>
+        <v>321.6509434570969</v>
       </c>
       <c r="X17" t="n">
         <v>369.731100678469</v>
@@ -23777,19 +23777,19 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
-        <v>157.6450804554009</v>
+        <v>133.3437862061145</v>
       </c>
       <c r="F18" t="n">
-        <v>145.0692123933839</v>
+        <v>117.4791871330677</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>109.7534919028945</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>84.64541897618032</v>
       </c>
       <c r="I18" t="n">
-        <v>61.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -23819,13 +23819,13 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>147.0207711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>172.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>197.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23847,10 +23847,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>151.8319801819373</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C19" t="n">
-        <v>145.2243534724417</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D19" t="n">
         <v>148.6154730182124</v>
@@ -23895,28 +23895,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
         <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
-        <v>227.9455894282815</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>258.7290040961748</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>224.5476180635119</v>
       </c>
       <c r="W19" t="n">
         <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>225.7096553890372</v>
+        <v>203.2608960285278</v>
       </c>
       <c r="Y19" t="n">
-        <v>190.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="20">
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
@@ -23941,7 +23941,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>203.0173518716929</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23950,7 +23950,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23971,10 +23971,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
         <v>209.0200695862453</v>
@@ -23983,16 +23983,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>308.77727522772</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X20" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y20" t="n">
         <v>386.2379386560536</v>
@@ -24008,28 +24008,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>44.19126966260332</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24062,16 +24062,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>225.3235108047433</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -24090,7 +24090,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
-        <v>15.42850543284433</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E22" t="n">
         <v>146.4339626465692</v>
@@ -24147,7 +24147,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
@@ -24163,25 +24163,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.7338416634806</v>
+        <v>170.4484560200385</v>
       </c>
       <c r="C23" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>329.5173872279562</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
@@ -24208,10 +24208,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
         <v>209.0200695862453</v>
@@ -24229,7 +24229,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
         <v>386.2379386560536</v>
@@ -24242,7 +24242,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>172.7084989883157</v>
@@ -24263,7 +24263,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>20.35782233292231</v>
       </c>
       <c r="J24" t="n">
         <v>0.7465913262578567</v>
@@ -24296,7 +24296,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>170.4068831286993</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -24305,10 +24305,10 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -24369,7 +24369,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
@@ -24378,7 +24378,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24403,19 +24403,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>270.8892792984027</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>113.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>299.4691724331683</v>
       </c>
       <c r="F26" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
         <v>339.4748021157671</v>
@@ -24424,7 +24424,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24460,7 +24460,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>59.63878728529269</v>
+        <v>35.82600002105686</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -24527,7 +24527,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
@@ -24536,19 +24536,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24612,7 +24612,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T28" t="n">
-        <v>227.9455894282815</v>
+        <v>94.7586218429135</v>
       </c>
       <c r="U28" t="n">
         <v>286.3190293564909</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24640,22 +24640,22 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>339.4748021157671</v>
+        <v>318.2910467450428</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
@@ -24682,31 +24682,31 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>198.932670063531</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,13 +24716,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>48.72576195918364</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -24737,7 +24737,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1.493982823607183</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -24852,7 +24852,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24889,7 +24889,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24919,31 +24919,31 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>19.64806958624538</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>8.095849564131356</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>171.2379386560536</v>
+        <v>183.9432522271564</v>
       </c>
     </row>
     <row r="33">
@@ -24953,31 +24953,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>138.2326529540896</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0.9360167816828238</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,7 +25001,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
@@ -25013,13 +25013,13 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>205.6826957773044</v>
@@ -25056,10 +25056,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25074,10 +25074,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>71.32518834398849</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
         <v>177.2933913771695</v>
@@ -25098,7 +25098,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366913</v>
       </c>
       <c r="Y34" t="n">
         <v>218.5846533520948</v>
@@ -25111,13 +25111,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>150.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>337.1201481309901</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25135,7 +25135,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25159,7 +25159,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25171,16 +25171,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>327.7522584701349</v>
+        <v>148.0239245254684</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>133.8469710343848</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>154.3371029954408</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="36">
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
         <v>172.7084989883157</v>
@@ -25202,19 +25202,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>113.0033812467288</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>130.6708380328942</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25247,19 +25247,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25284,7 +25284,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H37" t="n">
         <v>162.2271725074396</v>
@@ -25335,7 +25335,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>92.5226878036691</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y37" t="n">
         <v>218.5846533520948</v>
@@ -25354,25 +25354,25 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>214.4983586414191</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>235.5744035704686</v>
       </c>
       <c r="H38" t="n">
-        <v>124.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25405,19 +25405,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>112.3582607871067</v>
       </c>
       <c r="W38" t="n">
-        <v>349.240968717413</v>
+        <v>133.8469710343848</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="39">
@@ -25433,7 +25433,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>8.043802205194538</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
@@ -25448,7 +25448,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>1.27154177815332</v>
       </c>
       <c r="J39" t="n">
         <v>0.7465913262578567</v>
@@ -25475,13 +25475,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
         <v>225.9413820809748</v>
@@ -25496,7 +25496,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25551,7 +25551,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>177.2933913771695</v>
@@ -25563,7 +25563,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25575,7 +25575,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y40" t="n">
-        <v>218.5846533520948</v>
+        <v>171.5597290184211</v>
       </c>
     </row>
     <row r="41">
@@ -25588,7 +25588,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>151.8486281536646</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25603,10 +25603,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>126.0505384984242</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25639,22 +25639,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>10.09584956413136</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>38.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>327.7522584701349</v>
+        <v>136.8197930290423</v>
       </c>
       <c r="W41" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>192.1113998930138</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>173.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25667,22 +25667,22 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>101.9379296723033</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
@@ -25712,10 +25712,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>113.0166351309089</v>
       </c>
       <c r="T42" t="n">
         <v>200.1647286948216</v>
@@ -25724,16 +25724,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25797,13 +25797,13 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U43" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
-        <v>118.9506757384599</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
         <v>286.522998336591</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350372.4996985703</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350372.4996985703</v>
+        <v>350057.1643459357</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350372.4996985704</v>
+        <v>350057.1643459359</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352018.7110648652</v>
+        <v>351692.9620346287</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506958.3588577134</v>
+        <v>506968.6860557797</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506958.3588577134</v>
+        <v>506968.6860557797</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506958.3588577134</v>
+        <v>506968.6860557795</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506958.3588577134</v>
+        <v>506968.6860557797</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488167.0194589256</v>
+        <v>506968.6860557795</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488167.0194589256</v>
+        <v>488451.7788506226</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488167.0194589256</v>
+        <v>488451.7788506226</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486721.5318128649</v>
+        <v>487028.1657216361</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64504.44331886783</v>
+        <v>64504.44331886782</v>
       </c>
       <c r="C2" t="n">
-        <v>64504.44331886784</v>
+        <v>64504.44331886782</v>
       </c>
       <c r="D2" t="n">
-        <v>68921.32712272141</v>
+        <v>64504.44331886782</v>
       </c>
       <c r="E2" t="n">
-        <v>68921.3271227214</v>
+        <v>68859.35582065162</v>
       </c>
       <c r="F2" t="n">
-        <v>68921.32712272138</v>
+        <v>68859.35582065163</v>
       </c>
       <c r="G2" t="n">
-        <v>69244.84892577637</v>
+        <v>69180.83107499294</v>
       </c>
       <c r="H2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="I2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.40351879937</v>
       </c>
       <c r="J2" t="n">
-        <v>99694.37396548247</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="K2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="L2" t="n">
-        <v>96001.40468548246</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="M2" t="n">
-        <v>96001.40468548248</v>
+        <v>96057.36704470613</v>
       </c>
       <c r="N2" t="n">
-        <v>96001.4046854825</v>
+        <v>96057.36704470612</v>
       </c>
       <c r="O2" t="n">
-        <v>95717.33012548248</v>
+        <v>95777.59137569285</v>
       </c>
       <c r="P2" t="n">
         <v>64504.44331886782</v>
@@ -26319,19 +26319,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>7649.655304310485</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16126.11082971696</v>
+        <v>16773.42562193359</v>
       </c>
       <c r="C4" t="n">
-        <v>16126.11082971696</v>
+        <v>16773.42562193358</v>
       </c>
       <c r="D4" t="n">
-        <v>17275.28476093077</v>
+        <v>16773.42562193359</v>
       </c>
       <c r="E4" t="n">
-        <v>17275.28476093077</v>
+        <v>17951.06575311121</v>
       </c>
       <c r="F4" t="n">
-        <v>17275.28476093077</v>
+        <v>17951.06575311121</v>
       </c>
       <c r="G4" t="n">
-        <v>17359.45786549053</v>
+        <v>18037.99796140191</v>
       </c>
       <c r="H4" t="n">
-        <v>25281.74016844437</v>
+        <v>26289.91179915752</v>
       </c>
       <c r="I4" t="n">
-        <v>25281.74016844437</v>
+        <v>26289.91179915752</v>
       </c>
       <c r="J4" t="n">
-        <v>25281.74016844437</v>
+        <v>26289.91179915752</v>
       </c>
       <c r="K4" t="n">
-        <v>25281.74016844437</v>
+        <v>26289.91179915751</v>
       </c>
       <c r="L4" t="n">
-        <v>24320.91253208073</v>
+        <v>26289.91179915752</v>
       </c>
       <c r="M4" t="n">
-        <v>24320.91253208073</v>
+        <v>25305.85634707758</v>
       </c>
       <c r="N4" t="n">
-        <v>24320.91253208073</v>
+        <v>25305.85634707758</v>
       </c>
       <c r="O4" t="n">
-        <v>24247.00271389891</v>
+        <v>25230.20039407688</v>
       </c>
       <c r="P4" t="n">
-        <v>16126.11082971696</v>
+        <v>16773.42562193359</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915087</v>
+        <v>14103.41769693424</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>14103.41769693424</v>
       </c>
       <c r="D6" t="n">
-        <v>8361.262361790643</v>
+        <v>14103.41769693424</v>
       </c>
       <c r="E6" t="n">
-        <v>50065.24236179062</v>
+        <v>41700.92105859637</v>
       </c>
       <c r="F6" t="n">
-        <v>50065.24236179061</v>
+        <v>49350.57636290687</v>
       </c>
       <c r="G6" t="n">
-        <v>49634.82106028585</v>
+        <v>48925.48501637045</v>
       </c>
       <c r="H6" t="n">
-        <v>2290.51679703809</v>
+        <v>1169.035813548515</v>
       </c>
       <c r="I6" t="n">
-        <v>59759.83379703808</v>
+        <v>58752.82295588018</v>
       </c>
       <c r="J6" t="n">
-        <v>59759.83379703811</v>
+        <v>58752.82295588021</v>
       </c>
       <c r="K6" t="n">
-        <v>59759.83379703808</v>
+        <v>58752.8229558802</v>
       </c>
       <c r="L6" t="n">
-        <v>58608.49215340172</v>
+        <v>58752.82295588021</v>
       </c>
       <c r="M6" t="n">
-        <v>58608.49215340175</v>
+        <v>57655.55563850043</v>
       </c>
       <c r="N6" t="n">
-        <v>58608.49215340176</v>
+        <v>57655.55563850042</v>
       </c>
       <c r="O6" t="n">
-        <v>58519.92741158357</v>
+        <v>57571.19575368151</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>47731.01769693424</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26910,31 +26910,31 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,22 +26947,22 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -26971,22 +26971,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,19 +27191,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,10 +35088,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35100,10 +35100,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,13 +35167,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,22 +35325,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>24.94949494949496</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35407,10 +35407,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M12" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -35419,10 +35419,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463084</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N15" t="n">
-        <v>24.94949494949496</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L18" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,16 +36121,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O21" t="n">
-        <v>113.3528627008217</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N24" t="n">
-        <v>226.3927858636066</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36516,7 +36516,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M26" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N26" t="n">
         <v>207.9338608153932</v>
@@ -36525,7 +36525,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36595,16 +36595,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>113.3528627008217</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>55.48829951343431</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36987,10 +36987,10 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
-        <v>83.05602671428214</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -37063,22 +37063,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>166.7292564376967</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>70.09551364982758</v>
@@ -37221,22 +37221,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
-        <v>150.7019698410586</v>
+        <v>143.5949833418711</v>
       </c>
       <c r="P35" t="n">
-        <v>90.5657124162131</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,22 +37300,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>166.7292564376967</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>9.971898209808115</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>70.09551364982758</v>
@@ -37458,19 +37458,19 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>104.0555615261842</v>
+        <v>96.94857502699675</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>142.4289093910907</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37537,22 +37537,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>166.7292564376967</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P39" t="n">
-        <v>184.4883612256069</v>
+        <v>9.971898209808115</v>
       </c>
       <c r="Q39" t="n">
         <v>70.09551364982758</v>
@@ -37695,19 +37695,19 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>212.2975967408112</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O41" t="n">
-        <v>150.7019698410586</v>
+        <v>47.19965394337734</v>
       </c>
       <c r="P41" t="n">
         <v>90.5657124162131</v>
@@ -37777,16 +37777,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>7.674627705892183</v>
+        <v>8.081749358897964</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
